--- a/Planning.xlsx
+++ b/Planning.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\angel\Desktop\Proyectos\FOC_BLDC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5CA817C-880F-4910-BD9C-C1CA045E03C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1C4CBD0-86FB-46C3-928B-77E25DF2399E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -69,9 +69,6 @@
     <t>3/30/2026                           Imprimir motor restante HIVE</t>
   </si>
   <si>
-    <t>4/2/2026                          Cortar cicloidales SS</t>
-  </si>
-  <si>
     <t>2 motors</t>
   </si>
   <si>
@@ -96,10 +93,13 @@
     <t>4/11/2026                              Deadline terminar CAD preliminar</t>
   </si>
   <si>
-    <t>4/1/2026                                       Modificar tolerancias CAD metal cicloidal</t>
-  </si>
-  <si>
     <t>4/29/2026                    Soldar PCB</t>
+  </si>
+  <si>
+    <t>4/16/2026                          Cortar cicloidales SS</t>
+  </si>
+  <si>
+    <t>4/15/2026                                       Modificar tolerancias CAD metal cicloidal</t>
   </si>
 </sst>
 </file>
@@ -211,10 +211,6 @@
     <dxf>
       <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
       <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -337,6 +333,10 @@
           <color indexed="64"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -352,16 +352,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8D81E00B-5F29-458D-BB8C-FFCD0B4998F0}" name="Table1" displayName="Table1" ref="A1:G10" totalsRowShown="0" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8D81E00B-5F29-458D-BB8C-FFCD0B4998F0}" name="Table1" displayName="Table1" ref="A1:G10" totalsRowShown="0" dataDxfId="7">
   <autoFilter ref="A1:G10" xr:uid="{8D81E00B-5F29-458D-BB8C-FFCD0B4998F0}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{0DAE059D-FA33-4AE7-A913-BA15DF9F29CC}" name="Monday" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{8DE90F34-EFE3-4C56-86A6-F72A5A400AAF}" name="Tuesday" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{D2292876-B791-4A4C-B202-D613EBB37C24}" name="Wednesday" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{C8A0B9AD-6A28-4F51-87A9-93CCD6FD28C9}" name="Thursday" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{F21EB69C-E06E-45E8-B1C1-FB269EEDAE2C}" name="Friday" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{0E889AE7-D224-490D-90A9-252745A2B637}" name="Saturday" dataDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{0EF080B5-3707-498E-BCF2-938300390344}" name="Sunday" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{0DAE059D-FA33-4AE7-A913-BA15DF9F29CC}" name="Monday" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{8DE90F34-EFE3-4C56-86A6-F72A5A400AAF}" name="Tuesday" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{D2292876-B791-4A4C-B202-D613EBB37C24}" name="Wednesday" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{C8A0B9AD-6A28-4F51-87A9-93CCD6FD28C9}" name="Thursday" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{F21EB69C-E06E-45E8-B1C1-FB269EEDAE2C}" name="Friday" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{0E889AE7-D224-490D-90A9-252745A2B637}" name="Saturday" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{0EF080B5-3707-498E-BCF2-938300390344}" name="Sunday" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -687,7 +687,7 @@
         <v>46103</v>
       </c>
       <c r="J2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K2" t="s">
         <v>8</v>
@@ -729,11 +729,11 @@
       <c r="B4" s="1">
         <v>46112</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>14</v>
+      <c r="C4" s="1">
+        <v>46113</v>
+      </c>
+      <c r="D4" s="1">
+        <v>46114</v>
       </c>
       <c r="E4" s="1">
         <v>46115</v>
@@ -759,16 +759,16 @@
         <v>46119</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D5" s="4">
         <v>46121</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G5" s="1">
         <v>46124</v>
@@ -776,19 +776,19 @@
     </row>
     <row r="6" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="1">
-        <v>46127</v>
-      </c>
-      <c r="D6" s="1">
-        <v>46128</v>
+        <v>19</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F6" s="1">
         <v>46130</v>
@@ -811,7 +811,7 @@
         <v>46135</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F7" s="1">
         <v>46137</v>
@@ -828,7 +828,7 @@
         <v>46140</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D8" s="1">
         <v>46142</v>

--- a/Planning.xlsx
+++ b/Planning.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\angel\Desktop\Proyectos\FOC_BLDC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1C4CBD0-86FB-46C3-928B-77E25DF2399E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F564CB2E-234E-409F-8E88-715C754874B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
   <si>
     <t>Monday</t>
   </si>
@@ -99,7 +99,10 @@
     <t>4/16/2026                          Cortar cicloidales SS</t>
   </si>
   <si>
-    <t>4/15/2026                                       Modificar tolerancias CAD metal cicloidal</t>
+    <t>4/6/2026                                       Terminar CAD para poner piezas a imprimir</t>
+  </si>
+  <si>
+    <t>4/7/2026                                     Modificar tolerancias CAD metal cicloidal</t>
   </si>
 </sst>
 </file>
@@ -752,11 +755,11 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B5" s="1">
-        <v>46119</v>
+      <c r="A5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>16</v>
@@ -781,8 +784,8 @@
       <c r="B6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>24</v>
+      <c r="C6" s="1">
+        <v>46127</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>23</v>
